--- a/dws-pipeline-analyzer/templates/变更清单_模板.xlsx
+++ b/dws-pipeline-analyzer/templates/变更清单_模板.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +30,6 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,10 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +135,51 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>模板</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>表级变化类型：表/视图下线、表/视图替换、表/视图主键变化、表/视图名称或者schema变化、平切、表/视图数据初始化（刷时间戳）、表/视图初始化（不刷时间戳）、表/视图数据归档、表/视图取消权限、表/视图数据硬删除</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>模板</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>字段变化类型：字段类型及长度变化、字段下线/删除、字段值语义变化、新增字段、字段名称变化、字段数据初始化（刷时间戳）、字段数据初始化（不刷时间戳）</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>模板</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>类型说明（可选）：补充每个变化类型的详细定义，用于报告翻译</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,8 +471,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -462,15 +508,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>表级变化类型：表/视图下线、表/视图替换、表/视图主键变化、表/视图名称或者schema变化、平切、表/视图数据初始化（刷时间戳）、表/视图初始化（不刷时间戳）、表/视图数据归档、表/视图取消权限、表/视图数据硬删除</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -480,8 +520,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -575,15 +635,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>字段变化类型：字段类型及长度变化、字段下线/删除、字段值语义变化、新增字段、字段名称变化、字段数据初始化（刷时间戳）、字段数据初始化（不刷时间戳）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -593,8 +647,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -608,14 +666,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>类型说明（可选）：补充每个变化类型的详细定义，用于报告翻译</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>